--- a/crates/forskscope-core/src/tests/fixtures/xlsx/chart_sheet_not_compared/new.xlsx
+++ b/crates/forskscope-core/src/tests/fixtures/xlsx/chart_sheet_not_compared/new.xlsx
@@ -70,34 +70,28 @@
   <c:chart>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Data!$A$1:$A$2</c:f>
+              <c:f>Data!$A$2</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="50010001"/>
         <c:axId val="50010002"/>
-      </c:lineChart>
+      </c:barChart>
       <c:catAx>
         <c:axId val="50010001"/>
         <c:scaling>
